--- a/data/trending_integrated_20261016_15.xlsx
+++ b/data/trending_integrated_20261016_15.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8870</v>
+        <v>8900</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+24.06%</t>
+          <t>'+24.48%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-1.12</v>
       </c>
       <c r="E2" t="n">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="F2" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="G2" t="n">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="H2" t="n">
         <v>0.72</v>
@@ -610,7 +610,7 @@
         <v>1.84</v>
       </c>
       <c r="O2" t="n">
-        <v>249388898085</v>
+        <v>252984000055</v>
       </c>
       <c r="P2" t="n">
         <v>9180</v>
@@ -626,12 +626,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>인수합병 기대감 및 공매도 상환 움직임 포착. 텐버거 가능성 언급. 거래량은 증가.</t>
+          <t>인수합병 기대감 및 공매도 상환 언급. 텐버거 가능성, 2차전지 대장주 편입 등 긍정적 전망. 거래량 증가와 함께 급등 이유 분석 시도.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8690</v>
+        <v>8780</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+21.54%</t>
+          <t>'+22.80%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.23</v>
       </c>
       <c r="E3" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F3" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G3" t="n">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="H3" t="n">
         <v>0.47</v>
@@ -693,7 +693,7 @@
         <v>8100</v>
       </c>
       <c r="L3" t="n">
-        <v>8800</v>
+        <v>8830</v>
       </c>
       <c r="M3" t="n">
         <v>7810</v>
@@ -702,7 +702,7 @@
         <v>0.7</v>
       </c>
       <c r="O3" t="n">
-        <v>68827226990</v>
+        <v>74639629330</v>
       </c>
       <c r="P3" t="n">
         <v>16200</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7840</v>
+        <v>7780</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+19.33%</t>
+          <t>'+18.42%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.26</v>
       </c>
       <c r="E4" t="n">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F4" t="n">
         <v>81</v>
       </c>
       <c r="G4" t="n">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="H4" t="n">
         <v>0.73</v>
@@ -794,7 +794,7 @@
         <v>0.99</v>
       </c>
       <c r="O4" t="n">
-        <v>83037529615</v>
+        <v>84163906505</v>
       </c>
       <c r="P4" t="n">
         <v>10300</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>정치적 이슈와 함께 군공항 이전 및 호남 반도체 관련 언급. 신고가 돌파 및 매수 권유.</t>
+          <t>군공항 이전 관련 및 정치 테마 언급. 신고가 돌파 및 8만원 가능성, 호남 반도체 관련 긍정적 전망. 투경 및 급락 주의 언급도 존재.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['군공항 이전', '호남 반도체']</t>
+          <t>['군공항', '정치 테마', '신고가']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,18 +843,18 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9400</v>
+        <v>9370</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+6.33%</t>
+          <t>'+6.00%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.77</v>
       </c>
       <c r="E5" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F5" t="n">
         <v>51</v>
@@ -886,7 +886,7 @@
         <v>14.37</v>
       </c>
       <c r="O5" t="n">
-        <v>94197351340</v>
+        <v>94824582580</v>
       </c>
       <c r="P5" t="n">
         <v>14350</v>
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>218500</v>
+        <v>10260</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+4.05%</t>
+          <t>'+3.32%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.18</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>800</v>
+        <v>71</v>
       </c>
       <c r="F6" t="n">
-        <v>492</v>
+        <v>35</v>
       </c>
       <c r="G6" t="n">
-        <v>1345</v>
+        <v>152</v>
       </c>
       <c r="H6" t="n">
-        <v>45.98</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,91 +963,91 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>210000</v>
+        <v>9930</v>
       </c>
       <c r="K6" t="n">
-        <v>215000</v>
+        <v>10100</v>
       </c>
       <c r="L6" t="n">
-        <v>222500</v>
+        <v>11100</v>
       </c>
       <c r="M6" t="n">
-        <v>210500</v>
+        <v>9860</v>
       </c>
       <c r="N6" t="n">
-        <v>46.16</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3363467264500</v>
+        <v>34148108210</v>
       </c>
       <c r="P6" t="n">
-        <v>374500</v>
+        <v>19380</v>
       </c>
       <c r="Q6" t="n">
-        <v>94500</v>
+        <v>3200</v>
       </c>
       <c r="R6" t="n">
-        <v>230000</v>
+        <v>-128000</v>
       </c>
       <c r="S6" t="n">
-        <v>-235000</v>
+        <v>-10000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>정치적 요인에 따른 외국인 이탈 및 주가 하락 우려 제기. 일부 긍정적 전망도 존재.</t>
+          <t>뉴스 노출에도 불구하고 주가 부진 지속. 외인 매수 후 매도 추정.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['외국인 이탈', '주가 전망']</t>
+          <t>['주가 부진', '기관 외국인', '매수 매도']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10290</v>
+        <v>216500</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+3.63%</t>
+          <t>'+3.10%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>-0.18</v>
       </c>
       <c r="E7" t="n">
-        <v>69</v>
+        <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>35</v>
+        <v>493</v>
       </c>
       <c r="G7" t="n">
-        <v>152</v>
+        <v>1356</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>45.98</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,60 +1055,60 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>9930</v>
+        <v>210000</v>
       </c>
       <c r="K7" t="n">
-        <v>10100</v>
+        <v>215000</v>
       </c>
       <c r="L7" t="n">
-        <v>11100</v>
+        <v>222500</v>
       </c>
       <c r="M7" t="n">
-        <v>9860</v>
+        <v>210500</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>46.16</v>
       </c>
       <c r="O7" t="n">
-        <v>33886894300</v>
+        <v>3453152088250</v>
       </c>
       <c r="P7" t="n">
-        <v>19380</v>
+        <v>374500</v>
       </c>
       <c r="Q7" t="n">
-        <v>3200</v>
+        <v>94500</v>
       </c>
       <c r="R7" t="n">
-        <v>-128000</v>
+        <v>230000</v>
       </c>
       <c r="S7" t="n">
-        <v>-10000</v>
+        <v>-235000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>뉴스 노출에도 불구하고 주가 부진 지속. 외인 매수 후 매도 추정.</t>
+          <t>정치적 이슈와 노조 관련 부정적 언급 다수. 외인 매도 및 역배열 이평선 언급. 일부 저항선 언급도 있으나 전반적 분위기 부정적.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['주가 부진', '기관 외국인', '매수 매도']</t>
+          <t>['외인 매도', '이평선', '정치적 이슈']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13480</v>
+        <v>13370</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+3.22%</t>
+          <t>'+2.37%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.21</v>
       </c>
       <c r="E8" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F8" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G8" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H8" t="n">
         <v>3.42</v>
@@ -1162,7 +1162,7 @@
         <v>3.21</v>
       </c>
       <c r="O8" t="n">
-        <v>47828794685</v>
+        <v>49108039490</v>
       </c>
       <c r="P8" t="n">
         <v>31500</v>
@@ -1207,83 +1207,83 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>진코스텍</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15390</v>
+        <v>64800</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.01%</t>
+          <t>'+2.37%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>262</v>
+        <v>162</v>
       </c>
       <c r="F9" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="G9" t="n">
-        <v>256</v>
+        <v>572</v>
       </c>
       <c r="H9" t="n">
-        <v>0.11</v>
+        <v>22.1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>14940</v>
+        <v>63300</v>
       </c>
       <c r="K9" t="n">
-        <v>14940</v>
+        <v>63900</v>
       </c>
       <c r="L9" t="n">
-        <v>16350</v>
+        <v>66400</v>
       </c>
       <c r="M9" t="n">
-        <v>14330</v>
+        <v>63500</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>22.11</v>
       </c>
       <c r="O9" t="n">
-        <v>81287931570</v>
+        <v>131709911800</v>
       </c>
       <c r="P9" t="n">
-        <v>30800</v>
+        <v>139200</v>
       </c>
       <c r="Q9" t="n">
-        <v>9810</v>
+        <v>57000</v>
       </c>
       <c r="R9" t="n">
-        <v>-2000</v>
+        <v>85000</v>
       </c>
       <c r="S9" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>상장 사기 및 공모가 뻥튀기 의혹 제기. 경영진 사퇴 요구 및 주가 부진에 대한 불만 표출.</t>
+          <t>뉴스케일파워 연계 상승 기대. 의무공개매수제도 청원 언급. 주주환원정책 요구.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['상장 사기', '공모가', '주가 부진']</t>
+          <t>['뉴스케일파워', '공개매수', '주주환원']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>250030</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>65200</v>
+        <v>41600</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.00%</t>
+          <t>'+2.09%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.01</v>
+        <v>0.13</v>
       </c>
       <c r="E10" t="n">
-        <v>157</v>
+        <v>306</v>
       </c>
       <c r="F10" t="n">
-        <v>93</v>
+        <v>143</v>
       </c>
       <c r="G10" t="n">
-        <v>569</v>
+        <v>1278</v>
       </c>
       <c r="H10" t="n">
-        <v>22.1</v>
+        <v>12.97</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>63300</v>
+        <v>40750</v>
       </c>
       <c r="K10" t="n">
-        <v>63900</v>
+        <v>40600</v>
       </c>
       <c r="L10" t="n">
-        <v>66400</v>
+        <v>42500</v>
       </c>
       <c r="M10" t="n">
-        <v>63500</v>
+        <v>40050</v>
       </c>
       <c r="N10" t="n">
-        <v>22.11</v>
+        <v>12.84</v>
       </c>
       <c r="O10" t="n">
-        <v>125762690550</v>
+        <v>19288176150</v>
       </c>
       <c r="P10" t="n">
-        <v>139200</v>
+        <v>69200</v>
       </c>
       <c r="Q10" t="n">
-        <v>57000</v>
+        <v>24150</v>
       </c>
       <c r="R10" t="n">
-        <v>85000</v>
+        <v>73000</v>
       </c>
       <c r="S10" t="n">
-        <v>2000</v>
+        <v>-8000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>뉴스케일파워 연계 상승 기대. 의무공개매수제도 청원 언급. 주주환원정책 요구.</t>
+          <t>CLASS1 발표 관련 기대감 및 FDA 승인 가능성 언급. 야간 선물 상승 언급. 일부 회의적인 시각과 과거 사례 언급도 존재.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['뉴스케일파워', '공개매수', '주주환원']</t>
+          <t>['CLASS1', 'FDA 승인', '발표']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,130 +1384,130 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>41750</v>
+        <v>18420</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.45%</t>
+          <t>'+1.38%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.13</v>
+        <v>-0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>299</v>
+        <v>71</v>
       </c>
       <c r="F11" t="n">
-        <v>141</v>
+        <v>42</v>
       </c>
       <c r="G11" t="n">
-        <v>1246</v>
+        <v>208</v>
       </c>
       <c r="H11" t="n">
-        <v>12.97</v>
+        <v>27.77</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>40750</v>
+        <v>18170</v>
       </c>
       <c r="K11" t="n">
-        <v>40600</v>
+        <v>18340</v>
       </c>
       <c r="L11" t="n">
-        <v>42500</v>
+        <v>18990</v>
       </c>
       <c r="M11" t="n">
-        <v>40050</v>
+        <v>18110</v>
       </c>
       <c r="N11" t="n">
-        <v>12.84</v>
+        <v>27.82</v>
       </c>
       <c r="O11" t="n">
-        <v>18028246300</v>
+        <v>55850082950</v>
       </c>
       <c r="P11" t="n">
-        <v>69200</v>
+        <v>35350</v>
       </c>
       <c r="Q11" t="n">
-        <v>24150</v>
+        <v>17210</v>
       </c>
       <c r="R11" t="n">
-        <v>73000</v>
+        <v>518000</v>
       </c>
       <c r="S11" t="n">
-        <v>-8000</v>
+        <v>172000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>C1 발표 및 FDA 승인에 대한 기대감. 임상 결과 및 규제 관련 불확실성 존재.</t>
+          <t>미증시 반등 및 유가 상승에 따른 강한 반등 예상. FDC, FLNG 수주 임박.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['C1 발표', 'FDA 승인', '임상 결과']</t>
+          <t>['미증시 반등', '수주 임박', '유가 상승']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>HMM</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18570</v>
+        <v>23500</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+2.20%</t>
+          <t>'+1.29%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.05</v>
+        <v>0.02</v>
       </c>
       <c r="E12" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F12" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="G12" t="n">
-        <v>199</v>
+        <v>484</v>
       </c>
       <c r="H12" t="n">
-        <v>27.77</v>
+        <v>9.23</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>18170</v>
+        <v>23200</v>
       </c>
       <c r="K12" t="n">
-        <v>18340</v>
+        <v>23250</v>
       </c>
       <c r="L12" t="n">
-        <v>18990</v>
+        <v>24250</v>
       </c>
       <c r="M12" t="n">
-        <v>18110</v>
+        <v>22900</v>
       </c>
       <c r="N12" t="n">
-        <v>27.82</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>53134348015</v>
+        <v>48745563050</v>
       </c>
       <c r="P12" t="n">
-        <v>35350</v>
+        <v>24950</v>
       </c>
       <c r="Q12" t="n">
-        <v>17210</v>
+        <v>17910</v>
       </c>
       <c r="R12" t="n">
-        <v>518000</v>
+        <v>635000</v>
       </c>
       <c r="S12" t="n">
-        <v>172000</v>
+        <v>27000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미증시 반등 및 유가 상승에 따른 강한 반등 예상. FDC, FLNG 수주 임박.</t>
+          <t>운항수익 폭등 및 3분기 영업이익 1조원 돌파 기대. SCFI 최고치 경신.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['미증시 반등', '수주 임박', '유가 상승']</t>
+          <t>['운항수익', '영업이익', 'SCFI']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>011200</t>
         </is>
       </c>
     </row>
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1286500</v>
+        <v>1278000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+1.94%</t>
+          <t>'+1.27%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1593,10 +1593,10 @@
         <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>451</v>
+        <v>469</v>
       </c>
       <c r="G13" t="n">
-        <v>1073</v>
+        <v>1123</v>
       </c>
       <c r="H13" t="n">
         <v>48.85</v>
@@ -1622,7 +1622,7 @@
         <v>49.02</v>
       </c>
       <c r="O13" t="n">
-        <v>4963461807500</v>
+        <v>5084406248500</v>
       </c>
       <c r="P13" t="n">
         <v>2987000</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>솔리다임 상장 철회 요구와 함께 주가 폭락 및 반도체 업황 둔화 우려가 지속됨.</t>
+          <t>솔리다임 우회상장 철회 요구 및 관련 부정적 전망. 급락 후 소폭 반등에 대한 불만. 반도체 섹터 전반의 약세 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['솔리다임', '주가 폭락', '반도체']</t>
+          <t>['솔리다임', '우회상장', '반도체']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1667,31 +1667,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HMM</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>23650</v>
+        <v>14730</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+1.94%</t>
+          <t>'+0.41%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.02</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>68</v>
+        <v>271</v>
       </c>
       <c r="F14" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="G14" t="n">
-        <v>471</v>
+        <v>664</v>
       </c>
       <c r="H14" t="n">
-        <v>9.23</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,143 +1699,143 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>23200</v>
+        <v>14670</v>
       </c>
       <c r="K14" t="n">
-        <v>23250</v>
+        <v>14800</v>
       </c>
       <c r="L14" t="n">
-        <v>24250</v>
+        <v>15270</v>
       </c>
       <c r="M14" t="n">
-        <v>22900</v>
+        <v>14700</v>
       </c>
       <c r="N14" t="n">
-        <v>9.210000000000001</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>47500131300</v>
+        <v>39540261345</v>
       </c>
       <c r="P14" t="n">
-        <v>24950</v>
+        <v>40350</v>
       </c>
       <c r="Q14" t="n">
-        <v>17910</v>
+        <v>3320</v>
       </c>
       <c r="R14" t="n">
-        <v>635000</v>
+        <v>-134000</v>
       </c>
       <c r="S14" t="n">
-        <v>27000</v>
+        <v>-61000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>운항수익 폭등 및 3분기 영업이익 1조원 돌파 기대. SCFI 최고치 경신.</t>
+          <t>단일판매 공급계약 체결 공시 및 수주 공시 언급. 주가조작 및 이재명 대통령 관련 정치적 언급이 있으나, 공시 사실 기반 긍정적 요소 일부 존재.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['운항수익', '영업이익', 'SCFI']</t>
+          <t>['공시', '수주', '주가조작']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>011200</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>진코스텍</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14850</v>
+        <v>14960</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+1.23%</t>
+          <t>'+0.13%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="F15" t="n">
-        <v>68</v>
+        <v>99</v>
       </c>
       <c r="G15" t="n">
-        <v>656</v>
+        <v>260</v>
       </c>
       <c r="H15" t="n">
-        <v>9.779999999999999</v>
+        <v>0.11</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>14670</v>
+        <v>14940</v>
       </c>
       <c r="K15" t="n">
-        <v>14800</v>
+        <v>14940</v>
       </c>
       <c r="L15" t="n">
-        <v>15270</v>
+        <v>16350</v>
       </c>
       <c r="M15" t="n">
-        <v>14800</v>
+        <v>14330</v>
       </c>
       <c r="N15" t="n">
-        <v>9.710000000000001</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>37592889345</v>
+        <v>82751473330</v>
       </c>
       <c r="P15" t="n">
-        <v>40350</v>
+        <v>30800</v>
       </c>
       <c r="Q15" t="n">
-        <v>3320</v>
+        <v>9810</v>
       </c>
       <c r="R15" t="n">
-        <v>-134000</v>
+        <v>-2000</v>
       </c>
       <c r="S15" t="n">
-        <v>-61000</v>
+        <v>3000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>주가 조작 의혹 제기 및 외인 보유율 관련 언급. 단일판매 공급계약 체결 공시 확인.</t>
+          <t>상장 사기 및 공모가 뻥튀기 의혹 제기. 경영진 사퇴 요구 및 주가 부진에 대한 불만 표출.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['주가 조작', '공시', '외인 보유율']</t>
+          <t>['상장 사기', '공모가', '주가 부진']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>250030</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
         <v>79</v>
       </c>
       <c r="G16" t="n">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="H16" t="n">
         <v>4.28</v>
@@ -1898,7 +1898,7 @@
         <v>1.78</v>
       </c>
       <c r="O16" t="n">
-        <v>75236888120</v>
+        <v>75819119145</v>
       </c>
       <c r="P16" t="n">
         <v>22450</v>
@@ -1943,79 +1943,79 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16300</v>
+        <v>26500</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-6.70%</t>
+          <t>'-10.02%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="E17" t="n">
-        <v>279</v>
+        <v>230</v>
       </c>
       <c r="F17" t="n">
-        <v>139</v>
+        <v>162</v>
       </c>
       <c r="G17" t="n">
-        <v>503</v>
+        <v>784</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>53.12</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>17470</v>
+        <v>29450</v>
       </c>
       <c r="K17" t="n">
-        <v>18710</v>
+        <v>29450</v>
       </c>
       <c r="L17" t="n">
-        <v>20300</v>
+        <v>29600</v>
       </c>
       <c r="M17" t="n">
-        <v>15850</v>
+        <v>26400</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>26.75</v>
       </c>
       <c r="O17" t="n">
-        <v>186257293685</v>
+        <v>202250300975</v>
       </c>
       <c r="P17" t="n">
-        <v>28800</v>
+        <v>32500</v>
       </c>
       <c r="Q17" t="n">
-        <v>15780</v>
+        <v>21000</v>
       </c>
       <c r="R17" t="n">
-        <v>4000</v>
+        <v>-456000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-315000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>저평가 및 반도체 테마 관련 언급 있으나, 주가 부진 지속. 급락 가능성 및 매수 기회 언급.</t>
+          <t>유증 가능성, 외인 매도, 급락에 대한 불안감 표현. 실적 발표 후 하락에 대한 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['반도체 테마', '주가 부진']</t>
+          <t>['유증', '외인 매도', '급락']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2028,86 +2028,86 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>26600</v>
+        <v>15640</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-9.68%</t>
+          <t>'-10.48%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>217</v>
+        <v>293</v>
       </c>
       <c r="F18" t="n">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="G18" t="n">
-        <v>758</v>
+        <v>547</v>
       </c>
       <c r="H18" t="n">
-        <v>53.22</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>29450</v>
+        <v>17470</v>
       </c>
       <c r="K18" t="n">
-        <v>29450</v>
+        <v>18710</v>
       </c>
       <c r="L18" t="n">
-        <v>29600</v>
+        <v>20300</v>
       </c>
       <c r="M18" t="n">
-        <v>26550</v>
+        <v>15500</v>
       </c>
       <c r="N18" t="n">
-        <v>26.75</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>190142820750</v>
+        <v>190442010095</v>
       </c>
       <c r="P18" t="n">
-        <v>32500</v>
+        <v>28800</v>
       </c>
       <c r="Q18" t="n">
-        <v>21000</v>
+        <v>15500</v>
       </c>
       <c r="R18" t="n">
-        <v>-456000</v>
+        <v>4000</v>
       </c>
       <c r="S18" t="n">
-        <v>-315000</v>
+        <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>외인 매도세 및 급락 지속, 유증 가능성 제기. 종가 소량 매수 의견.</t>
+          <t>반도체 테마 약세 및 저평가 논란. 신규주 상장 및 막판 투매 조심 언급. 주가 부진에 대한 답답함 표현.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['실적발표', '외인매도', '유증']</t>
+          <t>['반도체 테마', '저평가', '신규주']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>179880</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261016_15.xlsx
+++ b/data/trending_integrated_20261016_15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z18"/>
+  <dimension ref="A1:Z19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8900</v>
+        <v>8920</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+24.48%</t>
+          <t>'+24.76%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-1.12</v>
       </c>
       <c r="E2" t="n">
-        <v>237</v>
+        <v>252</v>
       </c>
       <c r="F2" t="n">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="G2" t="n">
-        <v>410</v>
+        <v>456</v>
       </c>
       <c r="H2" t="n">
         <v>0.72</v>
@@ -610,7 +610,7 @@
         <v>1.84</v>
       </c>
       <c r="O2" t="n">
-        <v>252984000055</v>
+        <v>256967501770</v>
       </c>
       <c r="P2" t="n">
         <v>9180</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>인수합병 기대감 및 공매도 상환 언급. 텐버거 가능성, 2차전지 대장주 편입 등 긍정적 전망. 거래량 증가와 함께 급등 이유 분석 시도.</t>
+          <t>인수합병 기대감 및 4년 묵은 물량 소화 언급. 공매도 상환 및 투자 주의 종목 지정 가능성 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['인수합병', '공매도', '텐버거']</t>
+          <t>['인수합병', '공매도', '투자주의']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8780</v>
+        <v>8640</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+22.80%</t>
+          <t>'+20.84%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.23</v>
       </c>
       <c r="E3" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F3" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G3" t="n">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="H3" t="n">
         <v>0.47</v>
@@ -702,7 +702,7 @@
         <v>0.7</v>
       </c>
       <c r="O3" t="n">
-        <v>74639629330</v>
+        <v>78488840045</v>
       </c>
       <c r="P3" t="n">
         <v>16200</v>
@@ -762,13 +762,13 @@
         <v>-0.26</v>
       </c>
       <c r="E4" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F4" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G4" t="n">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="H4" t="n">
         <v>0.73</v>
@@ -794,7 +794,7 @@
         <v>0.99</v>
       </c>
       <c r="O4" t="n">
-        <v>84163906505</v>
+        <v>84939552075</v>
       </c>
       <c r="P4" t="n">
         <v>10300</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9370</v>
+        <v>9420</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+6.00%</t>
+          <t>'+6.56%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.77</v>
       </c>
       <c r="E5" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F5" t="n">
         <v>51</v>
       </c>
       <c r="G5" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H5" t="n">
         <v>13.6</v>
@@ -886,7 +886,7 @@
         <v>14.37</v>
       </c>
       <c r="O5" t="n">
-        <v>94824582580</v>
+        <v>95404845060</v>
       </c>
       <c r="P5" t="n">
         <v>14350</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10260</v>
+        <v>10190</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+3.32%</t>
+          <t>'+2.62%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F6" t="n">
         <v>35</v>
       </c>
       <c r="G6" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>34148108210</v>
+        <v>34473979895</v>
       </c>
       <c r="P6" t="n">
         <v>19380</v>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>216500</v>
+        <v>215250</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+3.10%</t>
+          <t>'+2.50%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1044,7 +1044,7 @@
         <v>493</v>
       </c>
       <c r="G7" t="n">
-        <v>1356</v>
+        <v>1305</v>
       </c>
       <c r="H7" t="n">
         <v>45.98</v>
@@ -1070,7 +1070,7 @@
         <v>46.16</v>
       </c>
       <c r="O7" t="n">
-        <v>3453152088250</v>
+        <v>3538673902750</v>
       </c>
       <c r="P7" t="n">
         <v>374500</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>정치적 이슈와 노조 관련 부정적 언급 다수. 외인 매도 및 역배열 이평선 언급. 일부 저항선 언급도 있으나 전반적 분위기 부정적.</t>
+          <t>증권 당국의 금리 관련 대책 논의 언급, 직원 상여금 지급 관련 주총 부결 운동 주장. 외국인 이탈 원인 분석 및 정부 정책 비판.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['외인 매도', '이평선', '정치적 이슈']</t>
+          <t>['주주총회', '상여금', '외국인']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,31 +1115,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13370</v>
+        <v>41650</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+2.37%</t>
+          <t>'+2.21%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.21</v>
+        <v>0.13</v>
       </c>
       <c r="E8" t="n">
-        <v>69</v>
+        <v>314</v>
       </c>
       <c r="F8" t="n">
-        <v>41</v>
+        <v>148</v>
       </c>
       <c r="G8" t="n">
-        <v>279</v>
+        <v>1304</v>
       </c>
       <c r="H8" t="n">
-        <v>3.42</v>
+        <v>12.97</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,235 +1147,235 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>13060</v>
+        <v>40750</v>
       </c>
       <c r="K8" t="n">
-        <v>13390</v>
+        <v>40600</v>
       </c>
       <c r="L8" t="n">
-        <v>13620</v>
+        <v>42500</v>
       </c>
       <c r="M8" t="n">
-        <v>12910</v>
+        <v>40050</v>
       </c>
       <c r="N8" t="n">
-        <v>3.21</v>
+        <v>12.84</v>
       </c>
       <c r="O8" t="n">
-        <v>49108039490</v>
+        <v>19870271900</v>
       </c>
       <c r="P8" t="n">
-        <v>31500</v>
+        <v>69200</v>
       </c>
       <c r="Q8" t="n">
-        <v>1640</v>
+        <v>24150</v>
       </c>
       <c r="R8" t="n">
-        <v>-102000</v>
+        <v>73000</v>
       </c>
       <c r="S8" t="n">
-        <v>-10000</v>
+        <v>-8000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>야간 선물 폭등 및 미국 장 반등 속 광통신 테마 강세. 13490원 돌파 및 만원대 안착 기대감 존재.</t>
+          <t>CLASS1 발표 임박 및 FDA 승인 기대감 상승. 7만원 이하 매도 금지 및 긍정적 호재 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['광통신', '야간선물', '미국장 반등']</t>
+          <t>['FDA승인', 'CLASS1', '호재']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>64800</v>
+        <v>13340</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+2.37%</t>
+          <t>'+2.14%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.01</v>
+        <v>0.21</v>
       </c>
       <c r="E9" t="n">
-        <v>162</v>
+        <v>69</v>
       </c>
       <c r="F9" t="n">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="G9" t="n">
-        <v>572</v>
+        <v>290</v>
       </c>
       <c r="H9" t="n">
-        <v>22.1</v>
+        <v>3.42</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>63300</v>
+        <v>13060</v>
       </c>
       <c r="K9" t="n">
-        <v>63900</v>
+        <v>13390</v>
       </c>
       <c r="L9" t="n">
-        <v>66400</v>
+        <v>13620</v>
       </c>
       <c r="M9" t="n">
-        <v>63500</v>
+        <v>12910</v>
       </c>
       <c r="N9" t="n">
-        <v>22.11</v>
+        <v>3.21</v>
       </c>
       <c r="O9" t="n">
-        <v>131709911800</v>
+        <v>49887599630</v>
       </c>
       <c r="P9" t="n">
-        <v>139200</v>
+        <v>31500</v>
       </c>
       <c r="Q9" t="n">
-        <v>57000</v>
+        <v>1640</v>
       </c>
       <c r="R9" t="n">
-        <v>85000</v>
+        <v>-102000</v>
       </c>
       <c r="S9" t="n">
-        <v>2000</v>
+        <v>-10000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>뉴스케일파워 연계 상승 기대. 의무공개매수제도 청원 언급. 주주환원정책 요구.</t>
+          <t>야간 선물 폭등 및 미국 장 반등 속 광통신 테마 강세. 13490원 돌파 및 만원대 안착 기대감 존재.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['뉴스케일파워', '공개매수', '주주환원']</t>
+          <t>['광통신', '야간선물', '미국장 반등']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>41600</v>
+        <v>64400</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.09%</t>
+          <t>'+1.74%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.13</v>
+        <v>-0.01</v>
       </c>
       <c r="E10" t="n">
-        <v>306</v>
+        <v>163</v>
       </c>
       <c r="F10" t="n">
-        <v>143</v>
+        <v>96</v>
       </c>
       <c r="G10" t="n">
-        <v>1278</v>
+        <v>581</v>
       </c>
       <c r="H10" t="n">
-        <v>12.97</v>
+        <v>22.1</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>40750</v>
+        <v>63300</v>
       </c>
       <c r="K10" t="n">
-        <v>40600</v>
+        <v>63900</v>
       </c>
       <c r="L10" t="n">
-        <v>42500</v>
+        <v>66400</v>
       </c>
       <c r="M10" t="n">
-        <v>40050</v>
+        <v>63500</v>
       </c>
       <c r="N10" t="n">
-        <v>12.84</v>
+        <v>22.11</v>
       </c>
       <c r="O10" t="n">
-        <v>19288176150</v>
+        <v>136490667050</v>
       </c>
       <c r="P10" t="n">
-        <v>69200</v>
+        <v>139200</v>
       </c>
       <c r="Q10" t="n">
-        <v>24150</v>
+        <v>57000</v>
       </c>
       <c r="R10" t="n">
-        <v>73000</v>
+        <v>85000</v>
       </c>
       <c r="S10" t="n">
-        <v>-8000</v>
+        <v>2000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>CLASS1 발표 관련 기대감 및 FDA 승인 가능성 언급. 야간 선물 상승 언급. 일부 회의적인 시각과 과거 사례 언급도 존재.</t>
+          <t>뉴스케일파워 상승 언급 및 두산에너빌리티의 낮은 Per에 대한 지적. 주주환원 정책 촉구 및 신뢰도 제로 비판.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['CLASS1', 'FDA 승인', '발표']</t>
+          <t>['뉴스케일파워', 'Per', '주주환원']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>HMM</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18420</v>
+        <v>23500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+1.38%</t>
+          <t>'+1.29%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.05</v>
+        <v>0.02</v>
       </c>
       <c r="E11" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F11" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="G11" t="n">
-        <v>208</v>
+        <v>501</v>
       </c>
       <c r="H11" t="n">
-        <v>27.77</v>
+        <v>9.23</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,38 +1423,38 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>18170</v>
+        <v>23200</v>
       </c>
       <c r="K11" t="n">
-        <v>18340</v>
+        <v>23250</v>
       </c>
       <c r="L11" t="n">
-        <v>18990</v>
+        <v>24250</v>
       </c>
       <c r="M11" t="n">
-        <v>18110</v>
+        <v>22900</v>
       </c>
       <c r="N11" t="n">
-        <v>27.82</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>55850082950</v>
+        <v>50060529150</v>
       </c>
       <c r="P11" t="n">
-        <v>35350</v>
+        <v>24950</v>
       </c>
       <c r="Q11" t="n">
-        <v>17210</v>
+        <v>17910</v>
       </c>
       <c r="R11" t="n">
-        <v>518000</v>
+        <v>635000</v>
       </c>
       <c r="S11" t="n">
-        <v>172000</v>
+        <v>27000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미증시 반등 및 유가 상승에 따른 강한 반등 예상. FDC, FLNG 수주 임박.</t>
+          <t>운항수익 폭등 및 3분기 영업이익 1조원 돌파 기대. SCFI 최고치 경신.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['미증시 반등', '수주 임박', '유가 상승']</t>
+          <t>['운항수익', '영업이익', 'SCFI']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>011200</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HMM</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>23500</v>
+        <v>18340</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+1.29%</t>
+          <t>'+0.94%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="E12" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="F12" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G12" t="n">
-        <v>484</v>
+        <v>212</v>
       </c>
       <c r="H12" t="n">
-        <v>9.23</v>
+        <v>27.77</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>23200</v>
+        <v>18170</v>
       </c>
       <c r="K12" t="n">
-        <v>23250</v>
+        <v>18340</v>
       </c>
       <c r="L12" t="n">
-        <v>24250</v>
+        <v>18990</v>
       </c>
       <c r="M12" t="n">
-        <v>22900</v>
+        <v>18110</v>
       </c>
       <c r="N12" t="n">
-        <v>9.210000000000001</v>
+        <v>27.82</v>
       </c>
       <c r="O12" t="n">
-        <v>48745563050</v>
+        <v>57852603735</v>
       </c>
       <c r="P12" t="n">
-        <v>24950</v>
+        <v>35350</v>
       </c>
       <c r="Q12" t="n">
-        <v>17910</v>
+        <v>17210</v>
       </c>
       <c r="R12" t="n">
-        <v>635000</v>
+        <v>518000</v>
       </c>
       <c r="S12" t="n">
-        <v>27000</v>
+        <v>172000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>운항수익 폭등 및 3분기 영업이익 1조원 돌파 기대. SCFI 최고치 경신.</t>
+          <t>미증시 반등 및 유가 상승에 따른 강한 반등 예상. FDC, FLNG 수주 임박.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['운항수익', '영업이익', 'SCFI']</t>
+          <t>['미증시 반등', '수주 임박', '유가 상승']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>011200</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1278000</v>
+        <v>1272000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+1.27%</t>
+          <t>'+0.79%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1593,10 +1593,10 @@
         <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="G13" t="n">
-        <v>1123</v>
+        <v>1244</v>
       </c>
       <c r="H13" t="n">
         <v>48.85</v>
@@ -1622,7 +1622,7 @@
         <v>49.02</v>
       </c>
       <c r="O13" t="n">
-        <v>5084406248500</v>
+        <v>5208013940000</v>
       </c>
       <c r="P13" t="n">
         <v>2987000</v>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>솔리다임 우회상장 철회 요구 및 관련 부정적 전망. 급락 후 소폭 반등에 대한 불만. 반도체 섹터 전반의 약세 언급.</t>
+          <t>솔리다임 우회 상장 철회 요구 및 주가 하락에 대한 불만 표출. 투자자들의 좌절감과 한국 증시 비관론.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['솔리다임', '우회상장', '반도체']</t>
+          <t>['우회상장', '주가하락', '솔리다임']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1667,83 +1667,83 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14730</v>
+        <v>20850</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+0.41%</t>
+          <t>'+0.48%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.07000000000000001</v>
+        <v>2.5</v>
       </c>
       <c r="E14" t="n">
-        <v>271</v>
+        <v>129</v>
       </c>
       <c r="F14" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="G14" t="n">
-        <v>664</v>
+        <v>328</v>
       </c>
       <c r="H14" t="n">
-        <v>9.779999999999999</v>
+        <v>4.28</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>14670</v>
+        <v>20750</v>
       </c>
       <c r="K14" t="n">
-        <v>14800</v>
+        <v>20500</v>
       </c>
       <c r="L14" t="n">
-        <v>15270</v>
+        <v>21550</v>
       </c>
       <c r="M14" t="n">
-        <v>14700</v>
+        <v>19440</v>
       </c>
       <c r="N14" t="n">
-        <v>9.710000000000001</v>
+        <v>1.78</v>
       </c>
       <c r="O14" t="n">
-        <v>39540261345</v>
+        <v>77630565145</v>
       </c>
       <c r="P14" t="n">
-        <v>40350</v>
+        <v>22450</v>
       </c>
       <c r="Q14" t="n">
-        <v>3320</v>
+        <v>6320</v>
       </c>
       <c r="R14" t="n">
-        <v>-134000</v>
+        <v>-49000</v>
       </c>
       <c r="S14" t="n">
-        <v>-61000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>단일판매 공급계약 체결 공시 및 수주 공시 언급. 주가조작 및 이재명 대통령 관련 정치적 언급이 있으나, 공시 사실 기반 긍정적 요소 일부 존재.</t>
+          <t>양자보안 및 금융권 해킹 증가 추세에 따른 수혜 기대감. 신규 납품 요청 및 연기금 매수 동향 확인.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.6</v>
+        <v>0.35</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['공시', '수주', '주가조작']</t>
+          <t>['양자보안', '해킹', '신규 납품']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14960</v>
+        <v>14950</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+0.13%</t>
+          <t>'+0.07%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F15" t="n">
         <v>99</v>
       </c>
       <c r="G15" t="n">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="H15" t="n">
         <v>0.11</v>
@@ -1806,7 +1806,7 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>82751473330</v>
+        <v>83785407365</v>
       </c>
       <c r="P15" t="n">
         <v>30800</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>상장 사기 및 공모가 뻥튀기 의혹 제기. 경영진 사퇴 요구 및 주가 부진에 대한 불만 표출.</t>
+          <t>상장 사기 및 공모가 뻥튀기 의혹 제기. 경영진 사퇴 요구 및 법적 심판 경고.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['상장 사기', '공모가', '주가 부진']</t>
+          <t>['상장사기', '공모가', '경영진']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1851,83 +1851,83 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>20350</v>
+        <v>14640</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.93%</t>
+          <t>'-0.20%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2.5</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>127</v>
+        <v>283</v>
       </c>
       <c r="F16" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="G16" t="n">
-        <v>327</v>
+        <v>674</v>
       </c>
       <c r="H16" t="n">
-        <v>4.28</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>20750</v>
+        <v>14670</v>
       </c>
       <c r="K16" t="n">
-        <v>20500</v>
+        <v>14800</v>
       </c>
       <c r="L16" t="n">
-        <v>21550</v>
+        <v>15270</v>
       </c>
       <c r="M16" t="n">
-        <v>19440</v>
+        <v>14630</v>
       </c>
       <c r="N16" t="n">
-        <v>1.78</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>75819119145</v>
+        <v>41650508315</v>
       </c>
       <c r="P16" t="n">
-        <v>22450</v>
+        <v>40350</v>
       </c>
       <c r="Q16" t="n">
-        <v>6320</v>
+        <v>3320</v>
       </c>
       <c r="R16" t="n">
-        <v>-49000</v>
+        <v>-134000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-61000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>양자보안 및 금융권 해킹 증가 추세에 따른 수혜 기대감. 신규 납품 요청 및 연기금 매수 동향 확인.</t>
+          <t>건설주 상승 전망과 함께 주가 조작 의혹 제기 및 이재명 대통령 관련 비판. 공시 기반 계약 체결 및 외인 보유율 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['양자보안', '해킹', '신규 납품']</t>
+          <t>['공시', '주가조작', '건설주']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1947,27 +1947,27 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>26500</v>
+        <v>26350</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-10.02%</t>
+          <t>'-10.53%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0.19</v>
       </c>
       <c r="E17" t="n">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="F17" t="n">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="G17" t="n">
-        <v>784</v>
+        <v>815</v>
       </c>
       <c r="H17" t="n">
-        <v>53.12</v>
+        <v>53.15</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1984,13 +1984,13 @@
         <v>29600</v>
       </c>
       <c r="M17" t="n">
-        <v>26400</v>
+        <v>26300</v>
       </c>
       <c r="N17" t="n">
         <v>26.75</v>
       </c>
       <c r="O17" t="n">
-        <v>202250300975</v>
+        <v>209505214100</v>
       </c>
       <c r="P17" t="n">
         <v>32500</v>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>유증 가능성, 외인 매도, 급락에 대한 불안감 표현. 실적 발표 후 하락에 대한 언급.</t>
+          <t>실적 발표 후 주가 하락에 대한 유증 가능성 및 의도적 하락 의혹 제기. 외인 매도 및 유튜버 투자 조언 주의.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['유증', '외인 매도', '급락']</t>
+          <t>['유증', '실적', '외국인']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>15640</v>
+        <v>15140</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-10.48%</t>
+          <t>'-13.34%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>293</v>
+        <v>324</v>
       </c>
       <c r="F18" t="n">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="G18" t="n">
-        <v>547</v>
+        <v>562</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -2076,19 +2076,19 @@
         <v>20300</v>
       </c>
       <c r="M18" t="n">
-        <v>15500</v>
+        <v>15050</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>190442010095</v>
+        <v>195598117135</v>
       </c>
       <c r="P18" t="n">
         <v>28800</v>
       </c>
       <c r="Q18" t="n">
-        <v>15500</v>
+        <v>15050</v>
       </c>
       <c r="R18" t="n">
         <v>4000</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>반도체 테마 약세 및 저평가 논란. 신규주 상장 및 막판 투매 조심 언급. 주가 부진에 대한 답답함 표현.</t>
+          <t>종목의 저평가 및 반도체 테마 언급과 함께 주가 상승 부진에 대한 답답함 토로. 매도 금지 및 주포에 대한 기대감.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['반도체 테마', '저평가', '신규주']</t>
+          <t>['반도체', '저평가', '주포']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2121,6 +2121,98 @@
       <c r="Z18" t="inlineStr">
         <is>
           <t>179880</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>우진엔텍</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>11170</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>'-20.95%</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>226</v>
+      </c>
+      <c r="F19" t="n">
+        <v>122</v>
+      </c>
+      <c r="G19" t="n">
+        <v>272</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>14130</v>
+      </c>
+      <c r="K19" t="n">
+        <v>11960</v>
+      </c>
+      <c r="L19" t="n">
+        <v>14450</v>
+      </c>
+      <c r="M19" t="n">
+        <v>9900</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="O19" t="n">
+        <v>40367363300</v>
+      </c>
+      <c r="P19" t="n">
+        <v>34900</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>9900</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-159000</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-53000</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>하한가 및 급락 반복에 대한 실망감 표출. 계약 수주에도 불구하고 주가 부진. 정상 종목임을 주장.</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>['하한가', '계약', '주가부진']</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>457550</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261016_15.xlsx
+++ b/data/trending_integrated_20261016_15.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8920</v>
+        <v>9010</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+24.76%</t>
+          <t>'+26.01%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-1.12</v>
       </c>
       <c r="E2" t="n">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="F2" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G2" t="n">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="H2" t="n">
         <v>0.72</v>
@@ -610,7 +610,7 @@
         <v>1.84</v>
       </c>
       <c r="O2" t="n">
-        <v>256967501770</v>
+        <v>259111278100</v>
       </c>
       <c r="P2" t="n">
         <v>9180</v>
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>우리로</t>
+          <t>서산</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8640</v>
+        <v>8030</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+20.84%</t>
+          <t>'+22.22%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.23</v>
+        <v>-0.26</v>
       </c>
       <c r="E3" t="n">
-        <v>97</v>
+        <v>147</v>
       </c>
       <c r="F3" t="n">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="G3" t="n">
-        <v>325</v>
+        <v>281</v>
       </c>
       <c r="H3" t="n">
-        <v>0.47</v>
+        <v>0.73</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,91 +687,91 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>7150</v>
+        <v>6570</v>
       </c>
       <c r="K3" t="n">
-        <v>8100</v>
+        <v>6850</v>
       </c>
       <c r="L3" t="n">
-        <v>8830</v>
+        <v>8540</v>
       </c>
       <c r="M3" t="n">
-        <v>7810</v>
+        <v>6630</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7</v>
+        <v>0.99</v>
       </c>
       <c r="O3" t="n">
-        <v>78488840045</v>
+        <v>85614561905</v>
       </c>
       <c r="P3" t="n">
-        <v>16200</v>
+        <v>10300</v>
       </c>
       <c r="Q3" t="n">
-        <v>1206</v>
+        <v>952</v>
       </c>
       <c r="R3" t="n">
-        <v>229000</v>
+        <v>-8000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>데이터 센터향 매출 및 중국 시장 개방 기대감 속 미국 양자컴퓨터 관련주로 분류. SPAD 200 미반영 및 9천원대 매물 소화 과제.</t>
+          <t>군공항 이전 관련 정치적 요인 언급 및 다음 주 1만원 이상 상승 전망. 일부는 7,900원 전량 매도.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['데이터 센터', '양자컴퓨터', '매물 소화']</t>
+          <t>['군공항 이전', '호남 반도체', '정치적 요인']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>046970</t>
+          <t>079650</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>서산</t>
+          <t>우리로</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7780</v>
+        <v>8720</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+18.42%</t>
+          <t>'+21.96%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.26</v>
+        <v>-0.23</v>
       </c>
       <c r="E4" t="n">
-        <v>146</v>
+        <v>99</v>
       </c>
       <c r="F4" t="n">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="G4" t="n">
-        <v>263</v>
+        <v>338</v>
       </c>
       <c r="H4" t="n">
-        <v>0.73</v>
+        <v>0.47</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,60 +779,60 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>6570</v>
+        <v>7150</v>
       </c>
       <c r="K4" t="n">
-        <v>6850</v>
+        <v>8100</v>
       </c>
       <c r="L4" t="n">
-        <v>8540</v>
+        <v>8830</v>
       </c>
       <c r="M4" t="n">
-        <v>6630</v>
+        <v>7810</v>
       </c>
       <c r="N4" t="n">
-        <v>0.99</v>
+        <v>0.7</v>
       </c>
       <c r="O4" t="n">
-        <v>84939552075</v>
+        <v>79324617165</v>
       </c>
       <c r="P4" t="n">
-        <v>10300</v>
+        <v>16200</v>
       </c>
       <c r="Q4" t="n">
-        <v>952</v>
+        <v>1206</v>
       </c>
       <c r="R4" t="n">
-        <v>-8000</v>
+        <v>229000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>군공항 이전 관련 및 정치 테마 언급. 신고가 돌파 및 8만원 가능성, 호남 반도체 관련 긍정적 전망. 투경 및 급락 주의 언급도 존재.</t>
+          <t>데이터 센터향 매출 및 중국 시장 개방 기대감 속 미국 양자컴퓨터 관련주로 분류. SPAD 200 미반영 및 9천원대 매물 소화 과제.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['군공항', '정치 테마', '신고가']</t>
+          <t>['데이터 센터', '양자컴퓨터', '매물 소화']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>079650</t>
+          <t>046970</t>
         </is>
       </c>
     </row>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9420</v>
+        <v>9450</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+6.56%</t>
+          <t>'+6.90%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.77</v>
       </c>
       <c r="E5" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F5" t="n">
         <v>51</v>
       </c>
       <c r="G5" t="n">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="H5" t="n">
         <v>13.6</v>
@@ -886,7 +886,7 @@
         <v>14.37</v>
       </c>
       <c r="O5" t="n">
-        <v>95404845060</v>
+        <v>95623262910</v>
       </c>
       <c r="P5" t="n">
         <v>14350</v>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10190</v>
+        <v>10270</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+2.62%</t>
+          <t>'+3.42%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -952,7 +952,7 @@
         <v>35</v>
       </c>
       <c r="G6" t="n">
-        <v>154</v>
+        <v>190</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>34473979895</v>
+        <v>34544483445</v>
       </c>
       <c r="P6" t="n">
         <v>19380</v>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>215250</v>
+        <v>215500</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+2.50%</t>
+          <t>'+2.62%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="G7" t="n">
-        <v>1305</v>
+        <v>1290</v>
       </c>
       <c r="H7" t="n">
         <v>45.98</v>
@@ -1070,7 +1070,7 @@
         <v>46.16</v>
       </c>
       <c r="O7" t="n">
-        <v>3538673902750</v>
+        <v>3837840915750</v>
       </c>
       <c r="P7" t="n">
         <v>374500</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>증권 당국의 금리 관련 대책 논의 언급, 직원 상여금 지급 관련 주총 부결 운동 주장. 외국인 이탈 원인 분석 및 정부 정책 비판.</t>
+          <t>직원 상여금 지급 부결 및 정치적 요인으로 인한 외국인 이탈 우려. 일부는 225,500원 저항선까지 상승 가능성을 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['주주총회', '상여금', '외국인']</t>
+          <t>['상여금', '외국인 이탈', '저항선']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>41650</v>
+        <v>41700</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+2.21%</t>
+          <t>'+2.33%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1133,10 +1133,10 @@
         <v>314</v>
       </c>
       <c r="F8" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G8" t="n">
-        <v>1304</v>
+        <v>1312</v>
       </c>
       <c r="H8" t="n">
         <v>12.97</v>
@@ -1162,7 +1162,7 @@
         <v>12.84</v>
       </c>
       <c r="O8" t="n">
-        <v>19870271900</v>
+        <v>20643056300</v>
       </c>
       <c r="P8" t="n">
         <v>69200</v>
@@ -1222,13 +1222,13 @@
         <v>0.21</v>
       </c>
       <c r="E9" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F9" t="n">
         <v>41</v>
       </c>
       <c r="G9" t="n">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="H9" t="n">
         <v>3.42</v>
@@ -1254,7 +1254,7 @@
         <v>3.21</v>
       </c>
       <c r="O9" t="n">
-        <v>49887599630</v>
+        <v>50270537670</v>
       </c>
       <c r="P9" t="n">
         <v>31500</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>64400</v>
+        <v>64600</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+1.74%</t>
+          <t>'+2.05%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.01</v>
       </c>
       <c r="E10" t="n">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="F10" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G10" t="n">
-        <v>581</v>
+        <v>609</v>
       </c>
       <c r="H10" t="n">
         <v>22.1</v>
@@ -1346,7 +1346,7 @@
         <v>22.11</v>
       </c>
       <c r="O10" t="n">
-        <v>136490667050</v>
+        <v>143011003450</v>
       </c>
       <c r="P10" t="n">
         <v>139200</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>뉴스케일파워 상승 언급 및 두산에너빌리티의 낮은 Per에 대한 지적. 주주환원 정책 촉구 및 신뢰도 제로 비판.</t>
+          <t>뉴스케일파워 상승 마감, 스페이스X 선택 관련 언급. 일부는 무개념 정부 및 금융위원회 비판.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['뉴스케일파워', 'Per', '주주환원']</t>
+          <t>['뉴스케일파워', '스페이스X', '정부 비판']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1406,13 +1406,13 @@
         <v>0.02</v>
       </c>
       <c r="E11" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F11" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G11" t="n">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="H11" t="n">
         <v>9.23</v>
@@ -1438,7 +1438,7 @@
         <v>9.210000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>50060529150</v>
+        <v>54052168650</v>
       </c>
       <c r="P11" t="n">
         <v>24950</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18340</v>
+        <v>18400</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.94%</t>
+          <t>'+1.27%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.05</v>
       </c>
       <c r="E12" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F12" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G12" t="n">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="H12" t="n">
         <v>27.77</v>
@@ -1530,7 +1530,7 @@
         <v>27.82</v>
       </c>
       <c r="O12" t="n">
-        <v>57852603735</v>
+        <v>63373615735</v>
       </c>
       <c r="P12" t="n">
         <v>35350</v>
@@ -1593,10 +1593,10 @@
         <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>474</v>
+        <v>497</v>
       </c>
       <c r="G13" t="n">
-        <v>1244</v>
+        <v>1352</v>
       </c>
       <c r="H13" t="n">
         <v>48.85</v>
@@ -1622,7 +1622,7 @@
         <v>49.02</v>
       </c>
       <c r="O13" t="n">
-        <v>5208013940000</v>
+        <v>5628145364000</v>
       </c>
       <c r="P13" t="n">
         <v>2987000</v>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>솔리다임 우회 상장 철회 요구 및 주가 하락에 대한 불만 표출. 투자자들의 좌절감과 한국 증시 비관론.</t>
+          <t>솔리다임 우회상장 철회 요구와 함께 한국 증시 및 최태원 회장에 대한 비판. 8일 연속 음봉 기록.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['우회상장', '주가하락', '솔리다임']</t>
+          <t>['솔리다임', '우회상장', '연속 음봉']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>20850</v>
+        <v>20900</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+0.48%</t>
+          <t>'+0.72%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>2.5</v>
       </c>
       <c r="E14" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F14" t="n">
         <v>80</v>
       </c>
       <c r="G14" t="n">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="H14" t="n">
         <v>4.28</v>
@@ -1714,7 +1714,7 @@
         <v>1.78</v>
       </c>
       <c r="O14" t="n">
-        <v>77630565145</v>
+        <v>78715860345</v>
       </c>
       <c r="P14" t="n">
         <v>22450</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>양자보안 및 금융권 해킹 증가 추세에 따른 수혜 기대감. 신규 납품 요청 및 연기금 매수 동향 확인.</t>
+          <t>양자보안 관련 신규 납품 요청 및 러브콜 쇄도, 농협/KDB 방어 성공 소식. 25,000원 상승 기대감.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['양자보안', '해킹', '신규 납품']</t>
+          <t>['양자보안', '신규 납품', '러브콜']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1759,83 +1759,83 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>진코스텍</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14950</v>
+        <v>14730</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+0.07%</t>
+          <t>'+0.41%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>267</v>
+        <v>291</v>
       </c>
       <c r="F15" t="n">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="G15" t="n">
-        <v>258</v>
+        <v>712</v>
       </c>
       <c r="H15" t="n">
-        <v>0.11</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>14940</v>
+        <v>14670</v>
       </c>
       <c r="K15" t="n">
-        <v>14940</v>
+        <v>14800</v>
       </c>
       <c r="L15" t="n">
-        <v>16350</v>
+        <v>15270</v>
       </c>
       <c r="M15" t="n">
-        <v>14330</v>
+        <v>14630</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>83785407365</v>
+        <v>42887681015</v>
       </c>
       <c r="P15" t="n">
-        <v>30800</v>
+        <v>40350</v>
       </c>
       <c r="Q15" t="n">
-        <v>9810</v>
+        <v>3320</v>
       </c>
       <c r="R15" t="n">
-        <v>-2000</v>
+        <v>-134000</v>
       </c>
       <c r="S15" t="n">
-        <v>3000</v>
+        <v>-61000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>상장 사기 및 공모가 뻥튀기 의혹 제기. 경영진 사퇴 요구 및 법적 심판 경고.</t>
+          <t>단일판매 공급 계약 체결 공시에도 주가 반응 미미. 정치적 요인 및 주가 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['상장사기', '공모가', '경영진']</t>
+          <t>['공시', '공급계약', '주가조작']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,90 +1844,90 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>250030</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>진코스텍</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14640</v>
+        <v>14950</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-0.20%</t>
+          <t>'+0.07%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="F16" t="n">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="G16" t="n">
-        <v>674</v>
+        <v>259</v>
       </c>
       <c r="H16" t="n">
-        <v>9.779999999999999</v>
+        <v>0.11</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>14670</v>
+        <v>14940</v>
       </c>
       <c r="K16" t="n">
-        <v>14800</v>
+        <v>14940</v>
       </c>
       <c r="L16" t="n">
-        <v>15270</v>
+        <v>16350</v>
       </c>
       <c r="M16" t="n">
-        <v>14630</v>
+        <v>14330</v>
       </c>
       <c r="N16" t="n">
-        <v>9.710000000000001</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>41650508315</v>
+        <v>83997024615</v>
       </c>
       <c r="P16" t="n">
-        <v>40350</v>
+        <v>30800</v>
       </c>
       <c r="Q16" t="n">
-        <v>3320</v>
+        <v>9810</v>
       </c>
       <c r="R16" t="n">
-        <v>-134000</v>
+        <v>-2000</v>
       </c>
       <c r="S16" t="n">
-        <v>-61000</v>
+        <v>3000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>건설주 상승 전망과 함께 주가 조작 의혹 제기 및 이재명 대통령 관련 비판. 공시 기반 계약 체결 및 외인 보유율 언급.</t>
+          <t>상장 사기 및 공모가 뻥튀기 의혹 제기. 경영진 사퇴 요구 및 법적 심판 경고.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['공시', '주가조작', '건설주']</t>
+          <t>['상장사기', '공모가', '경영진']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>250030</t>
         </is>
       </c>
     </row>
@@ -1958,16 +1958,16 @@
         <v>0.19</v>
       </c>
       <c r="E17" t="n">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="F17" t="n">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="G17" t="n">
-        <v>815</v>
+        <v>829</v>
       </c>
       <c r="H17" t="n">
-        <v>53.15</v>
+        <v>53.02</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         <v>26.75</v>
       </c>
       <c r="O17" t="n">
-        <v>209505214100</v>
+        <v>215675514550</v>
       </c>
       <c r="P17" t="n">
         <v>32500</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>실적 발표 후 주가 하락에 대한 유증 가능성 및 의도적 하락 의혹 제기. 외인 매도 및 유튜버 투자 조언 주의.</t>
+          <t>실적 발표 후 급락, 유상증자 가능성 및 외국인 탈출 시작 언급. 2달간 상승분을 이틀 만에 빼는 모습.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['유증', '실적', '외국인']</t>
+          <t>['실적 발표', '유상증자', '외국인 탈출']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>15140</v>
+        <v>15010</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-13.34%</t>
+          <t>'-14.08%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>324</v>
+        <v>337</v>
       </c>
       <c r="F18" t="n">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="G18" t="n">
-        <v>562</v>
+        <v>620</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -2076,19 +2076,19 @@
         <v>20300</v>
       </c>
       <c r="M18" t="n">
-        <v>15050</v>
+        <v>15010</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>195598117135</v>
+        <v>196185098195</v>
       </c>
       <c r="P18" t="n">
         <v>28800</v>
       </c>
       <c r="Q18" t="n">
-        <v>15050</v>
+        <v>15010</v>
       </c>
       <c r="R18" t="n">
         <v>4000</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>종목의 저평가 및 반도체 테마 언급과 함께 주가 상승 부진에 대한 답답함 토로. 매도 금지 및 주포에 대한 기대감.</t>
+          <t>급격한 하락세와 함께 '잡주'라는 비판. 시총 대비 저평가 주장 있으나, 가격 흐름 불안정.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['반도체', '저평가', '주포']</t>
+          <t>['급락', '저평가', '잡주']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>11170</v>
+        <v>11130</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-20.95%</t>
+          <t>'-21.23%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="F19" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G19" t="n">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="H19" t="n">
         <v>2.95</v>
@@ -2174,7 +2174,7 @@
         <v>2.95</v>
       </c>
       <c r="O19" t="n">
-        <v>40367363300</v>
+        <v>40571710100</v>
       </c>
       <c r="P19" t="n">
         <v>34900</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>하한가 및 급락 반복에 대한 실망감 표출. 계약 수주에도 불구하고 주가 부진. 정상 종목임을 주장.</t>
+          <t>하한가 기록 및 수주 계약 소식에도 주가 반응 미미. 상장 이래 최저가 기록.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['하한가', '계약', '주가부진']</t>
+          <t>['하한가', '수주 계약', '상장 이래 최저가']</t>
         </is>
       </c>
       <c r="X19" t="n">

--- a/data/trending_integrated_20261016_15.xlsx
+++ b/data/trending_integrated_20261016_15.xlsx
@@ -578,13 +578,13 @@
         <v>-1.12</v>
       </c>
       <c r="E2" t="n">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F2" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G2" t="n">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="H2" t="n">
         <v>0.72</v>
@@ -610,7 +610,7 @@
         <v>1.84</v>
       </c>
       <c r="O2" t="n">
-        <v>259111278100</v>
+        <v>259212640600</v>
       </c>
       <c r="P2" t="n">
         <v>9180</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>인수합병 기대감 및 4년 묵은 물량 소화 언급. 공매도 상환 및 투자 주의 종목 지정 가능성 언급.</t>
+          <t>인수합병 가능성 및 4년 묵은 물량에 대한 기대감. 뉴로메가 편입 사례를 언급하며 높은 상승 잠재력 시사.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['인수합병', '공매도', '투자주의']</t>
+          <t>['인수합병', '물량', '뉴로메가']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>-0.26</v>
       </c>
       <c r="E3" t="n">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="F3" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="G3" t="n">
-        <v>281</v>
+        <v>310</v>
       </c>
       <c r="H3" t="n">
         <v>0.73</v>
@@ -702,7 +702,7 @@
         <v>0.99</v>
       </c>
       <c r="O3" t="n">
-        <v>85614561905</v>
+        <v>85711146745</v>
       </c>
       <c r="P3" t="n">
         <v>10300</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>군공항 이전 관련 정치적 요인 언급 및 다음 주 1만원 이상 상승 전망. 일부는 7,900원 전량 매도.</t>
+          <t>군공항 이전 관련 기대감 및 정치인 언급. 동시호가 급등 및 투경 지정에 따른 추가 상승 전망.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['군공항 이전', '호남 반도체', '정치적 요인']</t>
+          <t>['군공항 이전', '동시호가', '투경']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -762,13 +762,13 @@
         <v>-0.23</v>
       </c>
       <c r="E4" t="n">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="F4" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G4" t="n">
-        <v>338</v>
+        <v>357</v>
       </c>
       <c r="H4" t="n">
         <v>0.47</v>
@@ -794,7 +794,7 @@
         <v>0.7</v>
       </c>
       <c r="O4" t="n">
-        <v>79324617165</v>
+        <v>79406829325</v>
       </c>
       <c r="P4" t="n">
         <v>16200</v>
@@ -854,13 +854,13 @@
         <v>-0.77</v>
       </c>
       <c r="E5" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F5" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G5" t="n">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="H5" t="n">
         <v>13.6</v>
@@ -886,7 +886,7 @@
         <v>14.37</v>
       </c>
       <c r="O5" t="n">
-        <v>95623262910</v>
+        <v>95635954260</v>
       </c>
       <c r="P5" t="n">
         <v>14350</v>
@@ -952,7 +952,7 @@
         <v>35</v>
       </c>
       <c r="G6" t="n">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>34544483445</v>
+        <v>34551384885</v>
       </c>
       <c r="P6" t="n">
         <v>19380</v>
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="G7" t="n">
-        <v>1290</v>
+        <v>1296</v>
       </c>
       <c r="H7" t="n">
         <v>45.98</v>
@@ -1070,7 +1070,7 @@
         <v>46.16</v>
       </c>
       <c r="O7" t="n">
-        <v>3837840915750</v>
+        <v>3838157485250</v>
       </c>
       <c r="P7" t="n">
         <v>374500</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>직원 상여금 지급 부결 및 정치적 요인으로 인한 외국인 이탈 우려. 일부는 225,500원 저항선까지 상승 가능성을 언급.</t>
+          <t>직원 상여금 지급 관련 주주 행동 촉구 및 정부 개입에 대한 비판. 외국인 이탈 원인으로 정치적 요인 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['상여금', '외국인 이탈', '저항선']</t>
+          <t>['상여금', '외국인 이탈', '정부 개입']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1130,13 +1130,13 @@
         <v>0.13</v>
       </c>
       <c r="E8" t="n">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F8" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G8" t="n">
-        <v>1312</v>
+        <v>1344</v>
       </c>
       <c r="H8" t="n">
         <v>12.97</v>
@@ -1162,7 +1162,7 @@
         <v>12.84</v>
       </c>
       <c r="O8" t="n">
-        <v>20643056300</v>
+        <v>20643890300</v>
       </c>
       <c r="P8" t="n">
         <v>69200</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>CLASS1 발표 임박 및 FDA 승인 기대감 상승. 7만원 이하 매도 금지 및 긍정적 호재 언급.</t>
+          <t>CLASS1 관련 공시 및 FDA 승인에 대한 강한 기대감. 7만원 이하 매도 금지 및 월요일 발표 가능성 시사.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['FDA승인', 'CLASS1', '호재']</t>
+          <t>['CLASS1', 'FDA 승인', '공시']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1222,13 +1222,13 @@
         <v>0.21</v>
       </c>
       <c r="E9" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F9" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G9" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H9" t="n">
         <v>3.42</v>
@@ -1254,7 +1254,7 @@
         <v>3.21</v>
       </c>
       <c r="O9" t="n">
-        <v>50270537670</v>
+        <v>50286972550</v>
       </c>
       <c r="P9" t="n">
         <v>31500</v>
@@ -1314,13 +1314,13 @@
         <v>-0.01</v>
       </c>
       <c r="E10" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F10" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G10" t="n">
-        <v>609</v>
+        <v>628</v>
       </c>
       <c r="H10" t="n">
         <v>22.1</v>
@@ -1346,7 +1346,7 @@
         <v>22.11</v>
       </c>
       <c r="O10" t="n">
-        <v>143011003450</v>
+        <v>143031287850</v>
       </c>
       <c r="P10" t="n">
         <v>139200</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>뉴스케일파워 상승 마감, 스페이스X 선택 관련 언급. 일부는 무개념 정부 및 금융위원회 비판.</t>
+          <t>뉴스케일파워 등 관련 종목 상승 속 주가 부진에 대한 불만. 정부 정책 비판 및 신용 매도 의견.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['뉴스케일파워', '스페이스X', '정부 비판']</t>
+          <t>['뉴스케일파워', '주가 부진', '정부 정책']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1406,13 +1406,13 @@
         <v>0.02</v>
       </c>
       <c r="E11" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F11" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G11" t="n">
-        <v>496</v>
+        <v>508</v>
       </c>
       <c r="H11" t="n">
         <v>9.23</v>
@@ -1438,7 +1438,7 @@
         <v>9.210000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>54052168650</v>
+        <v>54054659650</v>
       </c>
       <c r="P11" t="n">
         <v>24950</v>
@@ -1498,13 +1498,13 @@
         <v>-0.05</v>
       </c>
       <c r="E12" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F12" t="n">
         <v>45</v>
       </c>
       <c r="G12" t="n">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="H12" t="n">
         <v>27.77</v>
@@ -1530,7 +1530,7 @@
         <v>27.82</v>
       </c>
       <c r="O12" t="n">
-        <v>63373615735</v>
+        <v>63398179735</v>
       </c>
       <c r="P12" t="n">
         <v>35350</v>
@@ -1593,10 +1593,10 @@
         <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>497</v>
+        <v>510</v>
       </c>
       <c r="G13" t="n">
-        <v>1352</v>
+        <v>1555</v>
       </c>
       <c r="H13" t="n">
         <v>48.85</v>
@@ -1622,7 +1622,7 @@
         <v>49.02</v>
       </c>
       <c r="O13" t="n">
-        <v>5628145364000</v>
+        <v>5629452980000</v>
       </c>
       <c r="P13" t="n">
         <v>2987000</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>솔리다임 우회상장 철회 요구와 함께 한국 증시 및 최태원 회장에 대한 비판. 8일 연속 음봉 기록.</t>
+          <t>경영진 무능 및 솔리다임 상장 철회 요구. 한국 증시 전반에 대한 비관적 전망과 함께 정치적 요인 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['솔리다임', '우회상장', '연속 음봉']</t>
+          <t>['경영진', '솔리다임', '한국 증시']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1682,13 +1682,13 @@
         <v>2.5</v>
       </c>
       <c r="E14" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F14" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="G14" t="n">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="H14" t="n">
         <v>4.28</v>
@@ -1714,7 +1714,7 @@
         <v>1.78</v>
       </c>
       <c r="O14" t="n">
-        <v>78715860345</v>
+        <v>80237944645</v>
       </c>
       <c r="P14" t="n">
         <v>22450</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>양자보안 관련 신규 납품 요청 및 러브콜 쇄도, 농협/KDB 방어 성공 소식. 25,000원 상승 기대감.</t>
+          <t>양자보안 기술력 기반 신규 납품 요청 및 금융권 보안 투자 확대. 농협, KDB 등 방어 성공 사실 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['양자보안', '신규 납품', '러브콜']</t>
+          <t>['양자보안', '신규 납품', '보안 투자']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1774,13 +1774,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="F15" t="n">
         <v>75</v>
       </c>
       <c r="G15" t="n">
-        <v>712</v>
+        <v>725</v>
       </c>
       <c r="H15" t="n">
         <v>9.779999999999999</v>
@@ -1806,7 +1806,7 @@
         <v>9.710000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>42887681015</v>
+        <v>43055588285</v>
       </c>
       <c r="P15" t="n">
         <v>40350</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>단일판매 공급 계약 체결 공시에도 주가 반응 미미. 정치적 요인 및 주가 조작 의혹 제기.</t>
+          <t>수주 공시에도 불구하고 주가 미반영에 대한 불만. 주가 조작 의혹 및 특정 정치인 관련 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['공시', '공급계약', '주가조작']</t>
+          <t>['수주 공시', '주가 조작', '대차해지']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1866,7 +1866,7 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F16" t="n">
         <v>100</v>
@@ -1898,7 +1898,7 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>83997024615</v>
+        <v>84016340015</v>
       </c>
       <c r="P16" t="n">
         <v>30800</v>
@@ -1958,13 +1958,13 @@
         <v>0.19</v>
       </c>
       <c r="E17" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F17" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G17" t="n">
-        <v>829</v>
+        <v>849</v>
       </c>
       <c r="H17" t="n">
         <v>53.02</v>
@@ -1990,7 +1990,7 @@
         <v>26.75</v>
       </c>
       <c r="O17" t="n">
-        <v>215675514550</v>
+        <v>215833851700</v>
       </c>
       <c r="P17" t="n">
         <v>32500</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>실적 발표 후 급락, 유상증자 가능성 및 외국인 탈출 시작 언급. 2달간 상승분을 이틀 만에 빼는 모습.</t>
+          <t>실적 발표 후 큰 폭 하락에 대한 불신 표현. 유증 가능성 및 외인 매도 시작 추측. 항공주 투자 회의론 제기.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['실적 발표', '유상증자', '외국인 탈출']</t>
+          <t>['실적 발표', '유상증자', '외인 매도']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2050,13 +2050,13 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="F18" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G18" t="n">
-        <v>620</v>
+        <v>700</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -2082,7 +2082,7 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>196185098195</v>
+        <v>196384446005</v>
       </c>
       <c r="P18" t="n">
         <v>28800</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>급격한 하락세와 함께 '잡주'라는 비판. 시총 대비 저평가 주장 있으나, 가격 흐름 불안정.</t>
+          <t>주가 급락 및 저평가에 대한 답답함 토로. 반도체 테마 부진과 악덕 기업에 대한 경고.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['급락', '저평가', '잡주']</t>
+          <t>['주가 급락', '저평가', '반도체 테마']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F19" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G19" t="n">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="H19" t="n">
         <v>2.95</v>
@@ -2174,7 +2174,7 @@
         <v>2.95</v>
       </c>
       <c r="O19" t="n">
-        <v>40571710100</v>
+        <v>40586112320</v>
       </c>
       <c r="P19" t="n">
         <v>34900</v>
